--- a/output/pdf_financials_xlsx/MTLO.xlsx
+++ b/output/pdf_financials_xlsx/MTLO.xlsx
@@ -855,7 +855,7 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>0.01171</v>
+        <v>0.013869</v>
       </c>
       <c r="C9" s="3" t="n">
         <v>0.013444</v>
@@ -7292,16 +7292,16 @@
         </is>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0</v>
+        <v>-0.656522</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0</v>
+        <v>-1.05887</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0</v>
+        <v>-0.340284</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>11.982024</v>
+        <v>11.376172</v>
       </c>
       <c r="G118" s="3" t="n">
         <v>0</v>
@@ -61266,7 +61266,11 @@
           <t>Exploration and evaluation expenditures- net</t>
         </is>
       </c>
-      <c r="D531" t="inlineStr"/>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E531" t="inlineStr">
         <is>
           <t>-</t>
@@ -62864,7 +62868,11 @@
           <t>Exploration and evaluation expenditures‐ net</t>
         </is>
       </c>
-      <c r="D547" t="inlineStr"/>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E547" t="inlineStr">
         <is>
           <t>-</t>
@@ -64375,7 +64383,11 @@
           <t>Exploration and evaluation expenditures - net</t>
         </is>
       </c>
-      <c r="D562" t="inlineStr"/>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E562" t="inlineStr">
         <is>
           <t>-</t>
@@ -85793,12 +85805,16 @@
           <t>Royalty expense</t>
         </is>
       </c>
-      <c r="D778" t="inlineStr"/>
+      <c r="D778" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E778" s="5" t="n">
         <v>0.002159</v>
       </c>
       <c r="F778" s="5" t="n">
-        <v>-0.0006890000000000001</v>
+        <v>0.0006890000000000001</v>
       </c>
       <c r="G778" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/MTLO.xlsx
+++ b/output/pdf_financials_xlsx/MTLO.xlsx
@@ -1050,34 +1050,34 @@
         <v>0</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.009949</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.01289</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.029986</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.05406</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.009365999999999999</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.00535</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.02858</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.015488</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.007182</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>0.0023</v>
       </c>
     </row>
     <row r="13">
@@ -2000,34 +2000,34 @@
         <v>-2.127776</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>1.566243</v>
+        <v>1.556294</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-0.999421</v>
+        <v>-1.012311</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-5.957687</v>
+        <v>-5.987673</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-8.590449</v>
+        <v>-8.644508999999999</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-6.371444</v>
+        <v>-6.38081</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-8.226972</v>
+        <v>-8.232322</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-25.327945</v>
+        <v>-25.356525</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-5.758745</v>
+        <v>-5.774233</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-5.823995</v>
+        <v>-5.831177</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-13.020222</v>
+        <v>-13.022522</v>
       </c>
     </row>
     <row r="28">
@@ -2116,34 +2116,34 @@
         <v>-2.127776</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>1.566243</v>
+        <v>1.556294</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.876406</v>
+        <v>-0.889296</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-5.141359</v>
+        <v>-5.171345</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-7.177109</v>
+        <v>-7.231169</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-3.882266</v>
+        <v>-3.891632</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-5.916968</v>
+        <v>-5.922318</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-23.421995</v>
+        <v>-23.450575</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-3.83486</v>
+        <v>-3.850348</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-3.911889</v>
+        <v>-3.919071</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-12.036936</v>
+        <v>-12.039236</v>
       </c>
     </row>
     <row r="30">
@@ -2193,31 +2193,31 @@
         </is>
       </c>
       <c r="J30" s="3" t="n">
-        <v>-17.18444822004727</v>
+        <v>-17.43719356587604</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>-49.62916350050659</v>
+        <v>-49.91861617181901</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>-64.10246700094952</v>
+        <v>-64.58530477951346</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>-23.06549760371723</v>
+        <v>-23.12114331438115</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>-33.73451799886236</v>
+        <v>-33.76502005182157</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>-145.4848624775813</v>
+        <v>-145.6623860988445</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>-24.31330938221144</v>
+        <v>-24.41150450164519</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>-26.9218196252971</v>
+        <v>-26.97124651561758</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>-101.3882352802443</v>
+        <v>-101.4076083948928</v>
       </c>
     </row>
     <row r="31">
@@ -2378,43 +2378,43 @@
         <v>0.218238</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.034181</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.319846</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.224375</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.774672</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>2.141432</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>6.649302</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>2.900074</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>8.349904</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>4.853218</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>2.117652</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>7.613668</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>6.577858</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>2.756415</v>
       </c>
     </row>
     <row r="35">
@@ -2494,43 +2494,43 @@
         <v>0.218238</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.034181</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.319846</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.224375</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.774672</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>2.141432</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>6.649302</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>3</v>
+        <v>5.900074</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0.17</v>
+        <v>8.519904</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0.17</v>
+        <v>5.023218</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0.10143</v>
+        <v>2.219082</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0.10498</v>
+        <v>7.718648</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0.108391</v>
+        <v>6.686249</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0.110396</v>
+        <v>2.866811</v>
       </c>
     </row>
     <row r="37">
@@ -3190,43 +3190,43 @@
         <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.034482</v>
+        <v>0.000301</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.319846</v>
+        <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.224375</v>
+        <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.9744930000000001</v>
+        <v>0.199821</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>3.570207</v>
+        <v>1.428775</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>8.042589</v>
+        <v>1.393287</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>3.824214</v>
+        <v>0.92414</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>9.716737999999999</v>
+        <v>1.366834</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>6.721338</v>
+        <v>1.86812</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>4.897063</v>
+        <v>2.779411</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>8.594253</v>
+        <v>0.980585</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>7.418569</v>
+        <v>0.840711</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>4.381746</v>
+        <v>1.625331</v>
       </c>
     </row>
     <row r="49">
@@ -8541,7 +8541,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -29336,7 +29336,7 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
@@ -67252,7 +67252,7 @@
       </c>
       <c r="D591" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E591" t="inlineStr">
@@ -67345,7 +67345,7 @@
       </c>
       <c r="D592" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E592" t="inlineStr">
@@ -70079,7 +70079,7 @@
       </c>
       <c r="D620" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E620" t="inlineStr">
@@ -71578,7 +71578,7 @@
       </c>
       <c r="D635" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E635" t="inlineStr">
@@ -74285,7 +74285,7 @@
       </c>
       <c r="D662" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E662" t="inlineStr">
@@ -74386,7 +74386,7 @@
       </c>
       <c r="D663" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E663" t="inlineStr">
@@ -77320,7 +77320,7 @@
       </c>
       <c r="D693" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E693" t="inlineStr">
@@ -78332,7 +78332,7 @@
       </c>
       <c r="D703" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E703" t="inlineStr">
@@ -85506,7 +85506,7 @@
       </c>
       <c r="D775" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E775" s="5" t="n">

--- a/output/pdf_financials_xlsx/MTLO.xlsx
+++ b/output/pdf_financials_xlsx/MTLO.xlsx
@@ -2064,28 +2064,28 @@
         <v>0.123015</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0.8163280000000001</v>
+        <v>0.712429</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>1.41334</v>
+        <v>1.060067</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>2.489178</v>
+        <v>1.943599</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>2.310004</v>
+        <v>1.881624</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>1.90595</v>
+        <v>1.598356</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>1.923885</v>
+        <v>1.668263</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>1.912106</v>
+        <v>1.704269</v>
       </c>
       <c r="R28" s="3" t="n">
-        <v>0.983286</v>
+        <v>0.890872</v>
       </c>
     </row>
     <row r="29">
@@ -2122,28 +2122,28 @@
         <v>-0.889296</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-5.171345</v>
+        <v>-5.275244</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-7.231169</v>
+        <v>-7.584442</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-3.891632</v>
+        <v>-4.437211</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-5.922318</v>
+        <v>-6.350698</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-23.450575</v>
+        <v>-23.758169</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-3.850348</v>
+        <v>-4.10597</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-3.919071</v>
+        <v>-4.126908</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-12.039236</v>
+        <v>-12.13165</v>
       </c>
     </row>
     <row r="30">
@@ -2196,28 +2196,28 @@
         <v>-17.43719356587604</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>-49.91861617181901</v>
+        <v>-50.92154564212815</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>-64.58530477951346</v>
+        <v>-67.7405683856293</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>-23.12114331438115</v>
+        <v>-26.36256240239275</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>-33.76502005182157</v>
+        <v>-36.20735078951571</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>-145.6623860988445</v>
+        <v>-147.5729949427508</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>-24.41150450164519</v>
+        <v>-26.03216777772297</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>-26.97124651561758</v>
+        <v>-28.40159135041807</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>-101.4076083948928</v>
+        <v>-102.1860201414692</v>
       </c>
     </row>
     <row r="31">
@@ -6233,31 +6233,31 @@
         <v>0</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>0.123015</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>0.712429</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>1.060067</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>1.943599</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>0</v>
+        <v>1.881624</v>
       </c>
       <c r="O100" s="3" t="n">
-        <v>0</v>
+        <v>1.598356</v>
       </c>
       <c r="P100" s="3" t="n">
-        <v>0</v>
+        <v>1.668263</v>
       </c>
       <c r="Q100" s="3" t="n">
-        <v>0</v>
+        <v>1.704269</v>
       </c>
       <c r="R100" s="3" t="n">
-        <v>0</v>
+        <v>0.890872</v>
       </c>
     </row>
     <row r="101">
@@ -40888,7 +40888,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
@@ -44069,7 +44069,7 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
@@ -47954,7 +47954,7 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">

--- a/output/pdf_financials_xlsx/MTLO.xlsx
+++ b/output/pdf_financials_xlsx/MTLO.xlsx
@@ -1294,7 +1294,7 @@
         <v>-8.590449</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>-6.371444</v>
+        <v>-6.023897</v>
       </c>
       <c r="N16" s="3" t="n">
         <v>-8.226972</v>
@@ -1343,31 +1343,31 @@
         <v>-0</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>0.075436</v>
+        <v>-0.075436</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>0.545887</v>
+        <v>-0.545887</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>0.406902</v>
+        <v>-0.261325</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.347547</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>0.007663</v>
+        <v>-0.007663</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>0.138346</v>
+        <v>-0.138346</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>0.014847</v>
+        <v>-0.014847</v>
       </c>
       <c r="Q17" s="3" t="n">
-        <v>0.127732</v>
+        <v>-0.127732</v>
       </c>
       <c r="R17" s="3" t="n">
-        <v>-0.003456</v>
+        <v>0.003456</v>
       </c>
     </row>
     <row r="18">
@@ -1591,10 +1591,10 @@
         <v>-5.4118</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>-8.183547000000001</v>
+        <v>-6.385515</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>-6.371444</v>
+        <v>-6.051273</v>
       </c>
       <c r="N20" s="3" t="n">
         <v>-8.219309000000001</v>
@@ -2012,7 +2012,7 @@
         <v>-8.644508999999999</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-6.38081</v>
+        <v>-6.033263</v>
       </c>
       <c r="N27" s="3" t="n">
         <v>-8.232322</v>
@@ -2128,7 +2128,7 @@
         <v>-7.584442</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-4.437211</v>
+        <v>-4.089664</v>
       </c>
       <c r="N29" s="3" t="n">
         <v>-6.350698</v>
@@ -2202,7 +2202,7 @@
         <v>-67.7405683856293</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>-26.36256240239275</v>
+        <v>-24.29770015552994</v>
       </c>
       <c r="N30" s="3" t="n">
         <v>-36.20735078951571</v>
@@ -2257,10 +2257,10 @@
         <v>-9.162733792493631</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>-4.736679072304603</v>
+        <v>-3.042041225086139</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>-0</v>
+        <v>-5.769471157956386</v>
       </c>
       <c r="N31" s="3" t="n">
         <v>-0.09314484113960762</v>
@@ -4164,31 +4164,31 @@
         <v>0</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0</v>
+        <v>0.351762</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>0</v>
+        <v>0.486938</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>0</v>
+        <v>0.374627</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>0</v>
+        <v>1.558641</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>0</v>
+        <v>0.302843</v>
       </c>
       <c r="O64" s="3" t="n">
-        <v>0</v>
+        <v>0.828155</v>
       </c>
       <c r="P64" s="3" t="n">
-        <v>0</v>
+        <v>0.332013</v>
       </c>
       <c r="Q64" s="3" t="n">
-        <v>0</v>
+        <v>0.227962</v>
       </c>
       <c r="R64" s="3" t="n">
-        <v>0</v>
+        <v>0.090699</v>
       </c>
     </row>
     <row r="65">
@@ -4518,25 +4518,25 @@
         <v>0</v>
       </c>
       <c r="L70" s="3" t="n">
-        <v>0</v>
+        <v>0.253682</v>
       </c>
       <c r="M70" s="3" t="n">
-        <v>0</v>
+        <v>0.394048</v>
       </c>
       <c r="N70" s="3" t="n">
-        <v>0</v>
+        <v>0.296759</v>
       </c>
       <c r="O70" s="3" t="n">
-        <v>0</v>
+        <v>0.175721</v>
       </c>
       <c r="P70" s="3" t="n">
-        <v>0</v>
+        <v>0.197923</v>
       </c>
       <c r="Q70" s="3" t="n">
-        <v>0</v>
+        <v>0.120129</v>
       </c>
       <c r="R70" s="3" t="n">
-        <v>0</v>
+        <v>0.087384</v>
       </c>
     </row>
     <row r="71">
@@ -4576,25 +4576,25 @@
         <v>1.033775</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>1.22233</v>
+        <v>1.476012</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>0.219</v>
+        <v>0.613048</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>0.27</v>
+        <v>0.566759</v>
       </c>
       <c r="O71" s="3" t="n">
-        <v>8.764727000000001</v>
+        <v>8.940448</v>
       </c>
       <c r="P71" s="3" t="n">
-        <v>0</v>
+        <v>0.197923</v>
       </c>
       <c r="Q71" s="3" t="n">
-        <v>0.18</v>
+        <v>0.300129</v>
       </c>
       <c r="R71" s="3" t="n">
-        <v>0.3</v>
+        <v>0.387384</v>
       </c>
     </row>
     <row r="72">
@@ -4808,25 +4808,25 @@
         <v>1.963878</v>
       </c>
       <c r="L75" s="3" t="n">
-        <v>2.178292</v>
+        <v>1.92461</v>
       </c>
       <c r="M75" s="3" t="n">
-        <v>4.678104</v>
+        <v>4.284056</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>3.418505</v>
+        <v>3.121746</v>
       </c>
       <c r="O75" s="3" t="n">
-        <v>4.177369</v>
+        <v>4.001648</v>
       </c>
       <c r="P75" s="3" t="n">
-        <v>3.685829</v>
+        <v>3.487906</v>
       </c>
       <c r="Q75" s="3" t="n">
-        <v>2.246329</v>
+        <v>2.1262</v>
       </c>
       <c r="R75" s="3" t="n">
-        <v>1.926482</v>
+        <v>1.839098</v>
       </c>
     </row>
     <row r="76">
@@ -5120,25 +5120,25 @@
         <v>0.1867440025824747</v>
       </c>
       <c r="L80" s="3" t="n">
-        <v>0.163557089632256</v>
+        <v>0.1803631086411658</v>
       </c>
       <c r="M80" s="3" t="n">
-        <v>0.3701880636796781</v>
+        <v>0.3849825386389119</v>
       </c>
       <c r="N80" s="3" t="n">
-        <v>0.5170556882356143</v>
+        <v>0.5321379811848829</v>
       </c>
       <c r="O80" s="3" t="n">
-        <v>-7.775711692322015</v>
+        <v>-7.914346824120104</v>
       </c>
       <c r="P80" s="3" t="n">
-        <v>13.05465267239127</v>
+        <v>13.3225930473559</v>
       </c>
       <c r="Q80" s="3" t="n">
-        <v>-3.901992695825084</v>
+        <v>-3.940745598768465</v>
       </c>
       <c r="R80" s="3" t="n">
-        <v>-0.9680679658926109</v>
+        <v>-0.9735711566902965</v>
       </c>
     </row>
     <row r="81">
@@ -7133,7 +7133,7 @@
         <v>0</v>
       </c>
       <c r="J115" s="3" t="n">
-        <v>0</v>
+        <v>2.0242</v>
       </c>
       <c r="K115" s="3" t="n">
         <v>0</v>
@@ -9974,7 +9974,11 @@
           <t>Current portion of lease obligation 16</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>-</t>
@@ -20597,7 +20601,11 @@
           <t>Current portion of lease obligation 18</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr"/>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E124" t="inlineStr">
         <is>
           <t>-</t>
@@ -26835,7 +26843,11 @@
           <t>Current portion of lease obligation 4</t>
         </is>
       </c>
-      <c r="D186" t="inlineStr"/>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E186" t="inlineStr">
         <is>
           <t>-</t>
@@ -54978,7 +54990,11 @@
           <t>Proceeds from short-term investments</t>
         </is>
       </c>
-      <c r="D469" t="inlineStr"/>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E469" t="inlineStr">
         <is>
           <t>-</t>
@@ -68131,7 +68147,11 @@
           <t>Income tax recovery (expense) 9</t>
         </is>
       </c>
-      <c r="D600" t="inlineStr"/>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E600" t="inlineStr">
         <is>
           <t>-</t>
@@ -69293,7 +69313,11 @@
           <t>Income tax recovery 9</t>
         </is>
       </c>
-      <c r="D612" t="inlineStr"/>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E612" t="inlineStr">
         <is>
           <t>-</t>
@@ -70382,7 +70406,11 @@
           <t>Income tax recovery</t>
         </is>
       </c>
-      <c r="D623" t="inlineStr"/>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E623" t="inlineStr">
         <is>
           <t>-</t>
@@ -72372,7 +72400,11 @@
           <t>Income tax recovery 11</t>
         </is>
       </c>
-      <c r="D643" t="inlineStr"/>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E643" t="inlineStr">
         <is>
           <t>-</t>
@@ -72469,7 +72501,11 @@
           <t>Net loss from continuing operations</t>
         </is>
       </c>
-      <c r="D644" t="inlineStr"/>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E644" t="inlineStr">
         <is>
           <t>-</t>
@@ -75190,7 +75226,11 @@
           <t>Income tax recovery 11</t>
         </is>
       </c>
-      <c r="D671" t="inlineStr"/>
+      <c r="D671" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E671" t="inlineStr">
         <is>
           <t>-</t>
